--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45492</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45938</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45987</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45880</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46014</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45982</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46007</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>46128</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45994</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46052</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45842</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>46258</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45842</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>46052</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>46197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44504</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45322</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45576</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>45735</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>45735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>46083</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>45409</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45813</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>45726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>45840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44790</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>45735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>46034</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>45247</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45394</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>46134</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>46251</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>44460</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>45956</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>46136</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>45933</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>46043</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>46051</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45539</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45617</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>46184</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45247</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>44462</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>46262</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>45518</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45811</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44942</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45377</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44881</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44753</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44519</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44830</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44519</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44708</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44742</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44790</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44880</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>44672</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44739</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>44790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>44465</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>44774</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44817</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>44790</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>44827</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>44732</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44476</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>44477</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>44643</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>44754</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>44754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44812</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>44816</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45498</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44886</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>45443</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>45141</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>45617</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45078</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45726</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>45194</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>44791</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>44826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45183</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45530</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>45544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>44796</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>44957</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45315</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45689</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>45637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44648</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>45512</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45189</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45754</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45377</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>45689</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44925</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44862</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45111</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45576</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44469</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44728</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45222</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45530</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>45744</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>45258</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>45764</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45764</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45183</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>45665</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44820</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45531</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45646</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45666</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45463</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45240</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45254</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45440</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45063</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45811</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45691</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44880</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45884</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45182</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45776</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45806</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45443</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45888</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45888</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45689</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45888</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45890</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45890</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45516</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44798</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>46051</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45214</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45714</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45897</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44881</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45600</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45904</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45520</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45533</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>45909</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>45363</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45817</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>46141</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>45665</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>46021</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>44980</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45453</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>46079</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45238</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>44970</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45772</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>45933</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45932</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>45932</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45646</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>44972</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45939</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45939</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>45939</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>45772</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>46149</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45520</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45945</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>45601</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45945</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>45950</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>44980</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45952</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45956</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>45956</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44612</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45954</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45691</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45959</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45961</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45350</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45322</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>46154</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45596</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45964</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45965</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45965</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45965</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45309</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45966</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>45169</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45973</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45471</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44509</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>45972</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45974</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45712</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45604</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
         <v>44966</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45979</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45981</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45481</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>46154</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45890</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45986</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45987</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>46161</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45457</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45002</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46161</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45614</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45183</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45331</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45106</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45994</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44503</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>46164</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45315</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>46164</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45589</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44960</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>46002</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>46031</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         <v>46033</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>46034</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>46037</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>46036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>46174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>44546</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45147</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>46037</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45187</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>46042</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>46044</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>46049</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>46169</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>46048</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>46049</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45166</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>46051</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>46050</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>46168</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45644</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>46052</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45174</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44739</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>46057</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46058</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45582</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>45363</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>46058</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22946,7 +22946,7 @@
         <v>46062</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>44869</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>46041</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45666</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>46021</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         <v>45240</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23384,7 +23384,7 @@
         <v>45639</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>45749</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23530,7 +23530,7 @@
         <v>45673</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>44734</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>44805</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>46071</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45299</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45689</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45689</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45631</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>46062</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>46181</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45244</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>46183</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>44908</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45225</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>46084</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>46082</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>46184</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>44461</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>46082</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45169</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46090</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46188</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46188</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>46188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>44701</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45296</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>46190</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46094</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>46190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>46094</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>46094</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45775</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46094</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>46184</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26067,7 +26067,7 @@
         <v>45008</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>46188</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>46188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>46191</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>46191</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>46191</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46099</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45448</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>46195</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>46092</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>46106</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>46106</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>46197</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>46108</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44930</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45265</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>46199</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>46112</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>45471</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>46114</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>46113</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27655,7 +27655,7 @@
         <v>46119</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>46121</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>46120</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>46121</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>46120</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>46121</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>46120</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>46124</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28244,7 +28244,7 @@
         <v>46125</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28322,7 +28322,7 @@
         <v>46125</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>46128</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45372</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>46128</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>46127</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>46127</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>46127</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>46202</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>46128</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>46127</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45184</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>46204</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>46204</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45082</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>44867</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>44837</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>46135</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45754</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>44673</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45817</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45240</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45519</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>46139</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45940</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45222</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>44855</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>46204</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>46203</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46203</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46204</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45244</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44909</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45331</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30796,7 +30796,7 @@
         <v>45254</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45371</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>44930</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45244</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46252</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46252</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>46252</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45631</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>46253</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>46253</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46253</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>46253</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>46210</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>46253</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>46253</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>46210</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45735</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32097,7 +32097,7 @@
         <v>44960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>46212</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>46254</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>46212</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45247</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>46255</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>44931</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32618,7 +32618,7 @@
         <v>46199</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>46259</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>46259</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>45588</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45763</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>45169</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45491</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>46261</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45672</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45762</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45722</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>46262</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45700</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>46265</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45762</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>46266</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44916</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46034</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45215</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45215</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>46268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>46268</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>46268</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>46272</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>46272</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45783</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>45674</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>45783</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>45483</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>46272</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>46275</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>46275</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>46275</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>46275</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>46274</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>46231</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45492</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>44719</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>46276</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46276</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46281</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>46281</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46280</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>46280</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>46280</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>46280</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>46238</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>46281</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36267,7 +36267,7 @@
         <v>46281</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45793</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45688</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>46281</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45483</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45531</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>46258</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45798</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>46283</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>46283</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>45807</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45807</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>45811</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45811</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45695</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45819</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37460,7 +37460,7 @@
         <v>45824</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>45832</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37606,7 +37606,7 @@
         <v>45833</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45833</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45835</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>45840</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37898,7 +37898,7 @@
         <v>45840</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>45840</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>45846</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45854</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>45756</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>45860</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45754</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45868</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45876</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45876</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45532</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45401</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44802</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45208</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45699</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39028,7 +39028,7 @@
         <v>46035</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>46089</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45492</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44820</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45938</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>45987</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45880</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45982</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>46007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45994</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>46128</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45842</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>46052</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46052</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>45842</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>46197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45840</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>46042</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44504</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>46083</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45576</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45735</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45840</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45322</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45409</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45726</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44790</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45735</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>46134</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45394</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>46251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>46043</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>46051</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45933</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>45811</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46136</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45956</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45539</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45839</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46184</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45247</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46262</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45617</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>45518</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44942</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45377</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44881</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44753</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44519</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44519</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>44708</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44673</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44739</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>44742</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44880</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44672</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44739</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44790</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44465</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44774</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44817</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44790</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44732</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44748</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44477</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44643</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>44754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44816</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44812</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44811</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44739</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45363</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44837</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45315</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45533</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45512</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45588</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44880</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44862</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44546</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>45457</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>45443</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>45793</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45222</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45688</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45884</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45531</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>46034</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46033</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45888</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45888</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46031</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45377</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>46036</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>45516</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>46037</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45890</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45890</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>46037</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>46042</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45644</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45897</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>46044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45106</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>46050</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>46049</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>46048</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45491</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>46049</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45646</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45544</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>46052</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>46051</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45909</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>46058</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>46058</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>46057</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>45582</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>46041</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45666</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45639</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44734</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>45240</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45183</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45673</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>46071</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>46062</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>45689</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>46082</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45932</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45932</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>46082</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>46084</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45807</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45807</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45604</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>46090</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45933</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45772</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45939</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45939</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45939</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>46094</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>46094</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>46094</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45498</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44966</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45945</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45811</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45811</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>46099</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45085</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45082</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45945</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45950</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44701</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45184</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>46092</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45952</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>46106</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>46106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45954</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>46108</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45772</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45956</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45956</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>46112</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>46114</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45959</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45689</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45617</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>46113</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45299</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>46119</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45244</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>46120</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>46121</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>46121</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45964</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>46120</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>46120</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45961</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>46121</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45601</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46124</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46125</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45965</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45966</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>46127</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46127</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>46127</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45481</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>46127</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45637</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45695</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45972</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45166</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45973</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45974</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>46128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45631</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>46128</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45979</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>44869</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45981</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45986</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45631</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45817</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>46135</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>45672</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45987</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45776</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45806</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45994</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>44820</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>46139</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45646</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45225</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>46002</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45691</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45691</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44957</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45189</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45440</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45530</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45763</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45819</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45727</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45714</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45764</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45824</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>46051</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45940</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45735</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>46021</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45689</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45689</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45363</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45817</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>46141</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>46079</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>44972</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44908</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45832</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46149</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45833</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45350</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>46154</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>46154</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45833</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45835</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45890</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45222</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>46161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46161</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45840</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>45840</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45840</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45331</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45846</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46164</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>44960</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46164</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45854</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45371</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44909</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45247</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45860</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45756</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45520</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45530</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45754</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>46174</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45002</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>44925</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45868</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46168</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>46169</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>46181</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45471</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>44469</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>46183</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45443</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>46184</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>46190</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>46188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>46190</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>46191</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>46188</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46184</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>46191</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46188</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46191</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45876</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45876</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46195</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>46197</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>46199</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45331</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46203</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>46202</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45600</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>46203</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46204</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46204</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45532</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46204</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46204</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45078</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45372</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>46252</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46252</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44805</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45194</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46252</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46210</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>46210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44648</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>46254</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>46253</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>46253</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>46253</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45665</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45762</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46253</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>46253</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45244</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45147</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46255</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45700</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>46212</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46199</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44728</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44728</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>46212</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45183</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45183</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>46259</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>46259</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>46261</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45665</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46262</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45463</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>45169</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45187</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44867</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>46265</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45744</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45215</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45215</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46034</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45754</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46268</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45254</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45322</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45254</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>46268</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46272</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>46272</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>46272</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>44930</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>46231</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>44886</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>46274</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46275</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>46275</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>46276</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46276</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>46275</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>46275</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>46280</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>46280</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45775</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45265</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>46280</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>46280</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46281</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46281</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45315</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46281</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>46281</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45726</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>46238</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45520</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>46286</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45531</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>44916</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>46283</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>46283</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>44960</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46288</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44826</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44970</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44673</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44881</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45448</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>46289</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>44930</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>45111</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45596</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>46290</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45240</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45240</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44855</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>44796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45214</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45471</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45576</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>45689</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44980</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45063</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45238</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44931</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45614</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45589</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44980</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45141</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45169</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45169</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>44791</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45296</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>44612</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>44798</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45722</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45519</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44503</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45453</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>45666</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45754</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45712</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45258</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>45309</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45764</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45204</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45182</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45244</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45483</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45674</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>45783</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44719</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>45492</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45483</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45401</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>44802</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45208</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45699</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>46035</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>46089</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45492</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44820</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45938</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>45987</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>45880</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45982</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>45727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>46007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45994</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>46128</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45842</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>46052</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46052</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>45842</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>46197</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45840</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>46042</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44504</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>46083</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>45576</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>45735</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>45735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45840</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45322</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45813</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45409</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>45726</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44790</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>45735</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>46134</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45394</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>46251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>46043</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         <v>46051</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45933</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5217,7 +5217,7 @@
         <v>45811</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46136</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45956</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>45539</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45839</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46184</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45247</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>46262</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45617</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>45518</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44942</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45377</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44881</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44753</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>44519</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44519</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>44708</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44673</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44739</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>44742</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44790</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44880</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44672</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44739</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44790</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44465</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44774</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44614</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>44817</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>44790</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44732</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>44827</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44748</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44476</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44477</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44643</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>44754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44754</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44816</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44812</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44811</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44739</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45363</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44837</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45749</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45315</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45533</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45512</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45588</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44880</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44862</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44546</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>45457</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>45443</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>45793</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45222</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45688</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45884</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45531</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>46034</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>46033</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45888</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45888</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>46031</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>45888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>45377</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>46036</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>45516</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>46037</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45890</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45890</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>46037</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45174</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>46042</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45644</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45897</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>46044</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45106</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>46050</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>44509</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>46049</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>45904</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>46048</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45491</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>46049</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>45646</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45544</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>46052</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>46051</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45909</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>46058</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>46058</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>46057</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>45582</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>46062</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>46041</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45666</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45639</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44734</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>45240</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45183</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>46021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45673</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>46071</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>46062</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>45689</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>46082</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45932</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45932</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>46082</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>46084</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45807</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45807</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45604</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>46090</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45933</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>45772</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45939</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45939</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45939</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>46094</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>46094</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>46094</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45498</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44966</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>45945</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>45811</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>45811</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>46099</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45085</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45082</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45945</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45950</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44701</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45184</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>46092</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45952</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>46106</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>46106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45954</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>46108</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45772</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45956</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45956</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>46112</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>46114</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>45959</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45689</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45617</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>46113</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45299</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>46119</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45244</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>46120</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>46121</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>46121</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>45964</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>46120</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>46120</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45961</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>46121</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45965</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45601</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46124</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46125</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45965</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45966</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>46127</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>45965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46127</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>46127</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45481</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>46127</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45637</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45695</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45972</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45166</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45973</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45974</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>46128</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45631</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>46128</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45979</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>44869</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>46128</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45981</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45986</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45631</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45817</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>46135</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>45672</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45987</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45776</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45806</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45994</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>44820</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>46139</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45646</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45811</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>45225</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>46002</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45691</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45691</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>44957</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>45189</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45440</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45530</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>45763</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45819</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45727</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45714</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>45764</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45824</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>46051</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45940</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45735</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>46021</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45689</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45689</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>45363</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45817</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>46141</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>46079</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>44972</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44908</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45832</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46149</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45833</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45350</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>46154</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>46154</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45833</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45835</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45890</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45222</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>46161</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46161</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45840</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>45840</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45840</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45331</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45846</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46164</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>44960</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46164</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45854</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45371</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44909</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45247</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45860</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45756</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>45520</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24925,7 +24925,7 @@
         <v>45530</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45754</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>46174</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45002</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>44925</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45868</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>46168</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>46169</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>46181</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45471</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>44469</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>46183</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>45443</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>46184</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>46188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>46190</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>46188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>46190</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>46191</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>46188</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46184</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>46191</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46188</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46191</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45876</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45876</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46195</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>46197</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>46199</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45331</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46203</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>46202</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45600</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>46203</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46204</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46204</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45532</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>46204</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>46204</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45078</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45372</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>46252</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>46252</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44805</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45194</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>46252</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>46210</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>46210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>44648</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         <v>46254</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>46253</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>46253</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>46253</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45665</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45762</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46253</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46253</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>46253</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45244</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45147</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>46255</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45700</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>46212</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>46199</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44728</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44728</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>46212</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45183</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45183</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>46259</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>46259</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>46261</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45665</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46262</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45463</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>45169</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45187</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44867</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>46265</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45744</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46266</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>45215</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45215</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46034</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45754</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>46268</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46268</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45254</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45322</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45254</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>46268</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>46272</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31989,7 +31989,7 @@
         <v>46272</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>46272</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>44930</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32218,7 +32218,7 @@
         <v>46231</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>44886</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>46274</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>46275</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>46275</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>46276</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46276</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>46275</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>46275</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>46280</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>46280</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45775</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45265</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>46280</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>46280</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46281</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46281</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45315</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46281</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>46281</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45726</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>46238</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>45520</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>46286</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45531</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>44916</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>46283</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>46283</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45008</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>44960</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34508,7 +34508,7 @@
         <v>46288</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>44826</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44970</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44673</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44881</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45448</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>46289</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>44930</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>45111</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45596</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>46290</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45240</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35394,7 +35394,7 @@
         <v>45240</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>44855</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35540,7 +35540,7 @@
         <v>44796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45214</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45471</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45576</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>45689</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44980</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45063</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45238</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44931</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>45614</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45589</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>44980</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45141</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45169</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45169</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>44791</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45296</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>44612</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36879,7 +36879,7 @@
         <v>44798</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45722</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45519</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44503</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45453</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>45666</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45754</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45712</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45258</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>45309</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45764</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45204</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45182</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45244</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45483</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>45783</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45674</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>45783</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>44719</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>45492</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45483</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45401</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>44802</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45208</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45699</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>46035</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>46089</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45492</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45938</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45987</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45880</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46014</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45982</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46007</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>46128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46052</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45842</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45842</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>46052</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>46197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>45840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44504</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45322</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>45735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46083</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45576</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45840</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45409</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45813</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>45735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>46134</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45247</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45394</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>46251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>46051</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45811</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45956</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>46136</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>46184</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>46262</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45539</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45617</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45247</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>44942</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>45377</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44881</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44753</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44519</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44708</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44519</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44739</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44790</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44880</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44672</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44739</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44790</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44774</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44790</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44732</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>44827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>44748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>44476</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>44477</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>44643</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>44754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44816</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44812</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45443</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45498</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44886</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45141</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44957</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45617</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>45078</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45726</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>45194</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>45183</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44826</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44791</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>45544</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44796</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45315</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45884</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45689</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>45637</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>44648</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45888</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45888</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45888</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45890</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45890</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45897</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>46031</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>46033</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45793</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45512</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>46034</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>46037</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>46036</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>45904</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45754</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46037</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>45377</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>45688</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>45483</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>45909</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45531</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>46044</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>46049</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>46048</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45689</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>46049</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45798</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45530</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>46051</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>46050</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45807</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45807</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44925</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>46052</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>46057</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>46058</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>46058</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>44862</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46062</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45933</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45111</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>46041</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45932</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45932</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45666</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>46021</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45639</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45673</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45576</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44734</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>46071</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45939</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45939</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45939</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45939</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>46062</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45811</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45811</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45945</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45222</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44728</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44728</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45945</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45950</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>46084</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>46082</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45952</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>46082</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45744</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45695</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45956</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45258</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45956</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45954</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45959</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>46090</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>45183</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45961</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45764</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45764</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45964</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45965</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45665</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45965</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>46094</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>44820</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46094</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>46094</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45966</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45531</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45646</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>46094</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>46099</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45463</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45972</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45666</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>46092</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45819</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45979</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45981</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46106</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>46108</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>46112</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45986</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>46114</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45240</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>44811</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46113</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46119</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45254</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45824</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>46121</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>46120</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>46121</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>46120</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>46121</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>46120</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45063</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>46124</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>44880</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>46125</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45994</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46128</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46128</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46127</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>46127</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>46127</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45182</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>46128</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46127</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45443</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45832</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45689</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>46135</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45833</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45833</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45516</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>44798</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45835</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45817</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45214</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>46139</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45940</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45840</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45840</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45840</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44881</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45440</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45600</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45811</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45520</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45727</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45846</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45533</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45776</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45806</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45665</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>44980</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45453</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45854</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>46051</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45714</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45756</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45860</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45238</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>44970</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45772</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45754</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45646</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45363</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45817</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>46141</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45772</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45868</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45520</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>46021</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45601</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>46079</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44980</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>46149</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44612</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45691</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45350</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46154</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45322</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45596</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45309</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>46154</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45890</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>46161</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45169</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45471</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>44509</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45712</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45604</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45331</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44966</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46164</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>46164</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45876</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45876</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45481</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45457</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45002</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46174</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>46169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45532</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>46168</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45614</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45183</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45106</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>46181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>46183</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>44503</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>46184</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45315</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>46188</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46188</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45589</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>46188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>46190</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>44960</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>46184</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>46188</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>46188</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>46191</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>46191</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>46191</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45204</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45085</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>46195</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>46197</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46199</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46202</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46204</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>46204</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>46204</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>46203</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>46203</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>46204</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44546</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>46210</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45147</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>46210</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>46212</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45187</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46212</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>46199</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>46259</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>46259</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45166</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45644</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46261</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>46262</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45174</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>44739</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45363</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46265</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44869</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46034</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>45749</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44805</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45299</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>46268</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46268</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45689</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45689</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46268</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45631</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45244</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44908</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>46272</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46272</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45225</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46272</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46275</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46275</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>46275</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>46275</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46274</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>46231</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>46276</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>46276</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45169</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46281</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>46280</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>46280</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>46280</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>46280</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>46238</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>46281</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>46281</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44701</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45296</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45775</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45008</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>46283</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46283</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45448</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46286</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44930</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45265</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45471</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>46288</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46289</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45372</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45184</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45082</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>44867</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>46290</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>44837</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>46293</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45754</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>44673</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45240</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>46252</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>46252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45519</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46294</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46294</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>46293</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46252</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45222</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>46294</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>46294</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>46294</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>46253</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44855</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>46297</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45244</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>44909</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46254</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45331</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>46255</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>46253</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>46253</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>46253</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>46297</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>46253</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>46253</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45254</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45371</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44930</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45244</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45631</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45735</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44960</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45247</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>44931</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>45588</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45763</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45169</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45491</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45672</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45762</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45722</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45700</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>44916</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45215</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45215</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>45783</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45674</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45783</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45483</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>45492</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>44719</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45401</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44802</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45208</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45699</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>46035</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>46089</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45492</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45938</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45987</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45880</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46014</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45982</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>46007</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>45727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>46128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46052</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45842</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45842</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>46052</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>46197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>45840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44504</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45322</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>45735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46083</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45576</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45840</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45409</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45813</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>45735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>46134</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45247</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45394</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>46251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>46043</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>46051</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45811</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45956</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>46136</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>46184</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>46262</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>45539</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>45617</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>45247</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>44942</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>45377</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44881</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44753</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44519</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44830</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         <v>44708</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44519</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>44673</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44739</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44790</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44880</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44672</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44739</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44790</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44774</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>44790</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>44732</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>44827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>44748</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>44476</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>44477</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>44643</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>44754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44816</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>44812</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45443</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45498</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44886</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45141</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44957</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45617</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>45078</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45726</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>45194</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>45183</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44826</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44791</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>45544</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44796</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45315</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>45884</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45689</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>45637</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>44648</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>45888</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45888</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45888</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>45890</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45890</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45897</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>46031</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>46033</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45793</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45512</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>46034</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>46037</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>46036</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>45904</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45754</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46037</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>45377</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>45688</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>45483</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>45909</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11800,7 +11800,7 @@
         <v>45531</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>46044</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>46049</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>46048</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>45689</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>46049</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45798</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45530</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>46051</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>46050</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45807</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45807</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44925</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>46052</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>46057</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>46058</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>45582</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>46058</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>44862</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46062</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45933</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45111</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>46041</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45932</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45932</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45666</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>46021</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45639</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45673</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45576</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44734</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>46071</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45939</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45939</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45939</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45939</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>46062</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45811</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45811</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45945</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45222</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44728</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44728</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45945</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45950</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>46084</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>46082</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45952</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>46082</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45744</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45695</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45956</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45258</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45956</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>45954</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45959</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>46090</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>45183</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45961</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>45764</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45764</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45964</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45965</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45665</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45965</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45965</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>46094</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>44820</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46094</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>46094</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45966</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45531</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45646</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>46094</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>46099</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45463</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45972</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45666</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45974</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>46092</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45819</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45979</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45981</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46106</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>46108</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>46112</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45986</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>46114</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45240</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>44811</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46113</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46119</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45254</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45824</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>46121</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>46120</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>46121</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>46120</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>46121</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>46120</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45063</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>46124</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>44880</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>46125</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45994</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46128</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46128</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46127</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>46127</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>46127</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45182</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>46128</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46127</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>45443</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45832</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45689</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>46135</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45833</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45833</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45516</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>44798</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45835</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45817</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45214</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>46139</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45940</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45840</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45840</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45840</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44881</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21905,7 +21905,7 @@
         <v>45440</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         <v>45600</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45811</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45520</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45727</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45846</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45533</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45776</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45806</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45665</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>44980</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45453</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45854</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>46051</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45714</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45756</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45860</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45238</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>44970</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>45772</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45754</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>45646</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45363</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45817</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>46141</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>45772</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>45868</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45520</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>46021</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45601</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>46079</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>44980</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>46149</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>44612</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45691</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45350</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>46154</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45322</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45596</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45309</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>46154</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45890</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>46161</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45169</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45471</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>44509</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45712</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45604</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45331</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>44966</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46164</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>46164</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45876</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45876</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45481</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45457</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45002</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46174</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>46169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45532</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>46168</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45614</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45183</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45106</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>46181</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>46183</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>44503</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>46184</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45315</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>46188</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46188</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45589</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>46188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>46190</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>46190</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>44960</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>46184</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>46188</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>46188</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>46191</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>46191</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28056,7 +28056,7 @@
         <v>46191</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>45204</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45085</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>46195</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>46197</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46199</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46202</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46204</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>46204</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>46204</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>46203</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>46203</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>46204</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44546</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>46210</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45147</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>46210</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>46212</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45187</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46212</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>46199</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>46259</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>46259</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45166</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45644</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46261</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>46262</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45174</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>44739</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45363</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>46265</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44869</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46266</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46034</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>45749</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>44805</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45299</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>46268</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>46268</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45689</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45689</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46268</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45631</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45244</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44908</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>46272</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46272</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>45225</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46272</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46275</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>46275</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>46275</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>46275</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>46274</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>46231</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>46276</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>46276</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45169</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32455,7 +32455,7 @@
         <v>46281</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>46280</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>46280</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>46280</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>46280</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>46238</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>46281</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>46281</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33142,7 +33142,7 @@
         <v>44701</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45296</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>45775</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33361,7 +33361,7 @@
         <v>45008</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>46283</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46283</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45448</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46286</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>44930</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45265</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>45471</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>46288</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>46289</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45372</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45184</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45082</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>44867</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>46290</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>44837</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         <v>46293</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45754</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>44673</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45240</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>46252</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>46252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45519</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46294</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46294</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>46293</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>46252</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45222</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>46294</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>46294</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>46294</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>46253</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44855</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>46297</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>45244</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>44909</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46254</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45331</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>46255</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>46253</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>46253</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>46253</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>46297</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>46253</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>46253</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45254</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45371</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44930</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45244</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>45631</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45735</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>44960</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45247</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>44931</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>45588</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45763</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45169</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45491</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45672</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45762</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45722</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45700</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38042,7 +38042,7 @@
         <v>44916</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38120,7 +38120,7 @@
         <v>45215</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38193,7 +38193,7 @@
         <v>45215</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38266,7 +38266,7 @@
         <v>45783</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45674</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45783</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45483</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38558,7 +38558,7 @@
         <v>45492</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>44719</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45401</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38782,7 +38782,7 @@
         <v>44802</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45208</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45699</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>46035</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>46089</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45492</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45938</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45987</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45880</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46014</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45982</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46007</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>46128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45842</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>46052</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>46052</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45842</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>46197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>45840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44504</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45576</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45322</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45735</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>46083</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45409</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45813</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>46301</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44790</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>45394</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45735</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>45247</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>46134</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46034</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>46251</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45539</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45933</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45811</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45247</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>46136</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>45956</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>46043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>45617</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>46051</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>46184</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44942</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>45377</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44753</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44519</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44708</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>44742</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44790</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44880</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44672</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>44739</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44732</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44827</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44748</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44774</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44643</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44812</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>44816</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45363</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45589</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44980</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>45749</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44837</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45141</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45169</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45169</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44791</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45315</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>45296</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44960</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45512</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44612</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44811</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44739</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44798</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45532</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>44880</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45722</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44862</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>44546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>45519</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45457</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45443</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44503</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45884</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45453</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44909</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45247</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45888</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45888</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45520</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45888</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45530</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45222</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45754</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45712</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>44925</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45897</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>45309</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45377</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>45204</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45182</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>45516</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45904</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>45644</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45106</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45909</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45471</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44509</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45491</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45646</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45483</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45544</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45783</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45674</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45783</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45443</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44719</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45492</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45183</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45483</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45793</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45689</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45932</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45932</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45331</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45688</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45604</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45600</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45531</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45798</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45772</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45933</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45078</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45498</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44966</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45937</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45372</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45085</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45082</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44805</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45194</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45807</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45807</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44701</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45184</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45939</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44648</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45939</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45939</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45811</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45811</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>45945</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45695</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45762</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45945</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45772</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45244</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45147</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>45689</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45617</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45299</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45700</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45819</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45244</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>45601</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44728</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44728</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45183</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45481</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45637</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45952</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45832</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45166</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45956</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45956</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45959</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45833</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45833</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45835</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45964</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45631</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45961</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45665</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45463</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>44869</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45965</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>45966</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45840</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45840</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45840</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45965</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45631</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45187</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45672</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44867</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45846</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45972</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45744</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45974</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45215</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45215</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>44820</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>45646</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45854</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>45860</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45754</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45756</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45225</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45254</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45322</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45254</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45754</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45691</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45691</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44957</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45868</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45189</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45979</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>44930</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45530</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45763</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>44886</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45764</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45876</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45876</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>46094</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>46094</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45986</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45775</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45265</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45689</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45689</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>46092</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45315</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>46106</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45987</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45726</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>46108</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44972</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45520</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>44908</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>46114</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45531</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>46113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45994</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>46119</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>46120</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46121</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>46121</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>46120</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>46120</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>46121</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46124</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46125</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>46127</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46127</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46127</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46002</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>46127</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45008</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>46128</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>46128</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>46128</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44826</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>44970</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45817</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46135</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>44673</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44881</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45448</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>45776</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45806</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45111</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>46139</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45596</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45240</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45240</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44855</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44796</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45811</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45214</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>46034</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45440</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>46033</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45471</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>46031</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45576</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45727</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46036</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45714</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>46037</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>46042</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45689</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>46044</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>44980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>46051</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45063</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45940</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45238</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44931</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>45614</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>46021</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>46050</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>46049</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>46048</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>46049</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45363</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>46052</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>46051</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>46058</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>46058</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46057</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>46141</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45582</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46062</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>46079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>46041</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45666</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45639</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44734</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45240</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>46021</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>45673</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>46149</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>46071</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45350</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>46154</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>46154</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>46082</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>46082</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45890</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>46084</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>46090</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>46161</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>46094</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>46094</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45331</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>46164</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>46164</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>46174</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>46169</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>46181</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>46183</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46184</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>46188</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>46190</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46188</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46188</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46190</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>46191</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>46188</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>46184</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>46188</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>46191</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>46195</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>46197</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>46203</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>46202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>46203</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>46204</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>46204</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>46204</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>46204</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>46210</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>46210</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>46212</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46199</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46212</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>46265</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>46266</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>46034</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>46268</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>46268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>46268</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>46272</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>46272</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>46272</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>46231</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>46274</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>46275</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>46275</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>46276</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>46276</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>46275</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>46275</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>46280</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>46280</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>46280</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46280</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>46281</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>46281</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>46281</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>46281</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46238</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46286</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46283</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>46283</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>46288</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>46289</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>46290</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>46294</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>46293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>46294</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>46293</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>46294</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>46294</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>46294</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>46252</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>46253</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>46253</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46253</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46252</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46253</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>46253</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>46252</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>46300</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>46300</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>46297</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>46300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>46254</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46297</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>46062</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>46255</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>46300</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>46191</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>46302</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46259</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46259</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>46302</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>46262</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46304</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>46304</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46303</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46303</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>46303</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46261</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45890</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>45401</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>44802</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45208</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45699</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46035</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>46089</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45492</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45938</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45987</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45880</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46014</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>45982</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>45727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>46007</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45994</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>46128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45842</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>46052</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>46052</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45842</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>46197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>45840</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>44504</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>45576</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45840</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45322</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45735</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>46083</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45409</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45813</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>46301</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>44790</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>45394</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45735</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>45247</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>46134</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>46034</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>46251</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45539</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45933</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45811</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>45247</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>46136</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>45956</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
         <v>46043</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>45617</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>46051</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>46184</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44942</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>45377</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>44881</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44753</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44519</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44708</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44673</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>44742</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>44790</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44880</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44672</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>44739</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44790</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44732</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44827</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44748</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44774</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44643</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44812</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>44816</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>45363</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45589</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>44980</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>45749</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44837</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>45141</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45169</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45169</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44791</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45315</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>45296</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44960</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45512</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44612</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44811</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44739</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>44798</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45532</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>44880</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>45722</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44862</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>44546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>45519</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45457</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45443</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44503</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45884</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45453</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44909</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45247</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45888</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45666</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45888</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45520</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45888</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45530</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45222</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45754</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45712</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>45258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>44925</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>45897</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>45309</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45377</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>45204</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>45182</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45244</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>45516</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45904</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>45644</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>45106</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45909</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45471</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>44509</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45491</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45646</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45483</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45544</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45783</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45674</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45783</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45443</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44719</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45492</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45183</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45483</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45793</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45689</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45932</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45932</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45331</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45688</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45604</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45600</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45531</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>45798</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45772</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45933</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45078</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45498</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>44966</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45937</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45372</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45085</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45082</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44805</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45194</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45807</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>45807</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44701</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15820,7 +15820,7 @@
         <v>45184</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>45939</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>44648</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>45939</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>45939</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45811</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45811</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>45945</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45695</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45762</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45945</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45772</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45244</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45147</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>45689</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>45617</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>45299</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45700</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45819</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45244</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>45601</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44728</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44728</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45183</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>45481</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45637</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45952</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45832</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45166</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45956</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45956</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45959</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45833</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45833</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45835</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45964</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45631</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45961</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45665</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45463</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>44869</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45965</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>45966</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45840</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45840</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45840</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45965</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45631</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         <v>45187</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>45672</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44867</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45846</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45972</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>45744</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45974</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45215</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45215</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>44820</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>45646</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45854</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>45860</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45754</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45756</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45225</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45254</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45322</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45254</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45754</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
         <v>45691</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45691</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44957</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45868</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>45189</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>45979</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>44930</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45530</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45763</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>44886</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45764</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45876</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45876</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45981</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>46094</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>46094</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45986</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45735</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22769,7 +22769,7 @@
         <v>45775</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45265</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45689</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45689</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>46092</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45315</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>46106</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45987</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45726</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23436,7 +23436,7 @@
         <v>46108</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44972</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>45520</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>44908</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>46112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23806,7 +23806,7 @@
         <v>46114</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45531</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>46113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24030,7 +24030,7 @@
         <v>45994</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>46119</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>44916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>46120</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>46121</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>46121</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>46120</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>46120</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>46121</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46124</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46125</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>46127</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46127</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>46127</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>46002</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>46127</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45008</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>46128</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>44960</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>46128</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>46128</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44826</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>44970</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45817</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46135</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>44673</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44881</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>45448</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44930</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>45776</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45806</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45111</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>46139</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>45596</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26567,7 +26567,7 @@
         <v>45240</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45240</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44855</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44796</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45811</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45214</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>46034</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45440</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>46033</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45471</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>46031</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45576</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45727</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46036</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45714</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>46037</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>46042</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45689</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>46044</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>44980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28037,7 +28037,7 @@
         <v>46051</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         <v>45063</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45940</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45238</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44931</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28412,7 +28412,7 @@
         <v>45614</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>46021</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>46050</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>46049</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>46048</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>46049</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>45363</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>45817</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>46052</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>46051</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29157,7 +29157,7 @@
         <v>46058</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>46058</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46057</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>46141</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45582</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46062</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>46079</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29678,7 +29678,7 @@
         <v>46041</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45666</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>45639</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44734</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29970,7 +29970,7 @@
         <v>45240</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>46021</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>45673</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>46149</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>46071</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>45350</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>46154</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>46154</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>46082</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30632,7 +30632,7 @@
         <v>46082</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45890</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>46084</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>46090</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>46161</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>46094</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>46094</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45331</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31231,7 +31231,7 @@
         <v>46164</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>46164</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>46174</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31465,7 +31465,7 @@
         <v>46169</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>46181</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>46183</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46184</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>46188</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>46190</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46188</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46188</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>46190</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>46191</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>46188</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>46184</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>46188</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>46191</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>46195</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>46197</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>46199</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>46203</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>46202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>46203</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>46204</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>46204</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>46204</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>46204</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>46210</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>46210</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>46212</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>46199</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33614,7 +33614,7 @@
         <v>46212</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>46265</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>46266</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>46034</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>46268</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>46268</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>46268</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>46272</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34228,7 +34228,7 @@
         <v>46272</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>46272</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>46231</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>46274</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>46275</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>46275</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>46276</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>46276</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>46275</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>46275</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>46280</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>46280</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>46280</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35242,7 +35242,7 @@
         <v>46280</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>46281</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>46281</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>46281</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>46281</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>46238</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46286</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         <v>46283</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>46283</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>46288</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>46289</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>46290</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36153,7 +36153,7 @@
         <v>46294</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>46293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>46294</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>46293</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>46294</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>46294</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
         <v>46294</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>46252</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>46253</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>46253</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>46253</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37011,7 +37011,7 @@
         <v>46252</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37089,7 +37089,7 @@
         <v>46253</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37167,7 +37167,7 @@
         <v>46253</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>46253</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>46252</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>46300</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>46300</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>46297</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>46300</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>46254</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46297</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>46062</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>46255</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>46300</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>46191</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>46302</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46259</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46259</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>46302</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>46262</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46304</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>46304</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46303</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46303</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>46303</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46261</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45890</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>45401</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>44802</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45208</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45699</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46035</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>46089</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45492</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45938</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45987</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45880</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46303</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45982</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>46007</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>45727</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45994</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46128</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>46052</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45842</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>46052</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45842</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>44504</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45322</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45576</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46083</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45735</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45409</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45813</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>45726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>46301</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44790</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>45735</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>46034</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45247</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>46134</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45394</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>46251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45956</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>46136</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>45933</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46043</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>46051</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45539</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45617</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45247</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>45811</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44942</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45377</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44881</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44753</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44519</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44708</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44742</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44790</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44880</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44826</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44672</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44739</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44774</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44614</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44790</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44732</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44827</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44748</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44643</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>44754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44816</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44812</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45498</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>44886</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45443</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45141</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45617</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45726</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45078</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45194</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44791</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>45544</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45315</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44648</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44796</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45689</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45512</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45189</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>45754</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>45377</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45689</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45530</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44925</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44862</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45111</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>45576</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44728</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44728</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45744</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45258</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>45764</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45183</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45665</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44820</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45531</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45646</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45463</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45666</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45440</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45811</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45727</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45240</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45884</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45776</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45254</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45806</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45063</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44880</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45888</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45888</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45888</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>46051</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45714</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45182</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>45897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45443</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45689</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45363</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45817</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>46141</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45516</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44798</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>46021</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45214</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46079</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45909</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44881</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>45520</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>45533</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>46149</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45665</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44980</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45933</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45932</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45932</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45453</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45937</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45350</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45939</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45939</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45939</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>46154</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45238</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44970</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45772</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45945</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45950</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>45952</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45646</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>45956</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>45956</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>46154</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44972</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45890</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45961</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>46161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45772</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45520</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45964</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45965</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45965</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45601</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45966</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44980</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45974</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45331</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44612</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45691</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>46164</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>46164</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>45322</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45596</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45986</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45309</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45987</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>45169</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45471</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44509</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45712</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45604</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45994</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>44966</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45481</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>46002</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>45457</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>46174</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45002</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45614</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45183</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45106</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>46169</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>46031</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44503</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46033</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45315</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46034</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>46036</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46037</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45589</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>46042</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>44960</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>46044</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>46049</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46048</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46049</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>46051</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>46050</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>45204</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45085</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>46052</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46181</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>46183</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>46057</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46058</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45582</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>46058</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>46062</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46041</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>46184</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45666</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>46021</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45240</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45639</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45673</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>44734</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>46071</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>46188</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>46188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>46188</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>46084</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>46082</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46082</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46190</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>46090</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44546</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>46190</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45147</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45187</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>46184</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>46188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46188</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>46094</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>46094</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>46094</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>46191</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>46094</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45166</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>46092</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45644</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>46195</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45174</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46106</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44739</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>46108</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>46112</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45363</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>46114</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>44869</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>46113</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>46119</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46199</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>46121</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>46120</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>46121</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45749</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46120</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>46121</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44805</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>46120</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45299</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>46124</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45689</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45689</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>46125</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45631</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45244</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46128</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46128</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>46127</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>46127</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>46127</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>44908</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>46128</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>46127</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>46202</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46204</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>46204</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45225</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46135</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45817</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46204</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>46203</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46203</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>46204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>46139</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45940</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44701</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45296</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45775</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45008</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46210</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45448</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>46210</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>46212</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>46199</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44930</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45265</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>45471</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>46034</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>46272</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>46272</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46272</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45372</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>46275</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>46275</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46275</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45184</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46275</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>46274</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>46231</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45082</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44867</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44837</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45754</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>46276</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44673</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>46276</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45240</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45519</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>46280</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>46280</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>46280</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>46280</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>46238</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45222</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46281</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>44855</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>46281</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45244</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>44909</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>46283</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>46283</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45331</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>45254</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45371</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>44930</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45244</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>46286</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45631</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45735</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46288</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46289</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45247</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>44931</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45763</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45169</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>46290</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45491</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>46293</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45672</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45762</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45722</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45700</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>46252</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>46252</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46294</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>46294</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>46293</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>46252</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>46294</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>46294</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46294</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>46253</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>44916</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>46297</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>46254</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>46253</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>46253</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46253</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>46297</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46253</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46253</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46191</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45215</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45215</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>46300</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>46300</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>46062</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45783</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46300</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45674</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45783</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46255</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45483</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45492</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>44719</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46300</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46303</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>46259</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>46302</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>46303</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>46302</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46259</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45793</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45688</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46307</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45483</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>46262</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45531</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45890</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45798</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>46304</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>46304</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46191</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>46261</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>46308</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>46266</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>46309</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>46309</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46308</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45807</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45807</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>46308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>46265</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45811</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45811</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>45695</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>46268</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>46268</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45819</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45824</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>46268</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>45832</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>45833</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45833</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45835</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45840</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45840</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45840</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45846</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45854</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45756</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45860</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45754</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45868</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45876</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45876</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>45401</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44802</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45208</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45699</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>46035</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>46089</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45492</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45938</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45987</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45880</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46303</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45982</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>46007</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>45727</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45994</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>46128</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>46052</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45842</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>46052</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46197</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>45842</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>46042</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45840</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>44504</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45322</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45576</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>46083</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>45735</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45409</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>45813</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>45726</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>46301</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44790</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>45735</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>46034</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45247</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>46134</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45394</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>46251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45956</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>46136</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>45933</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>46043</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>46051</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>46184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>45539</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45617</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45247</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45518</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>45811</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>45839</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>44942</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45377</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>44881</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44753</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44519</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44708</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44742</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44790</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>44880</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44826</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44672</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44739</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44790</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44774</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>44614</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>44817</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>44790</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>44732</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44827</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44748</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44643</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>44754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44754</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44816</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44812</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45498</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>44886</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45443</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45141</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45617</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>45726</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45078</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45194</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>44791</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45183</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44826</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>45544</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45315</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44648</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44796</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45689</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45512</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45189</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>45754</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>45377</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45689</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45530</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44925</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>44862</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45111</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>45576</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44728</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44728</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45744</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45258</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>45764</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45183</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45665</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44820</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45531</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45646</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45463</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45666</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45532</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45440</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45811</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45727</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45240</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45884</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45776</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45254</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45806</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45063</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>45691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44880</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45888</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45888</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>45888</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>46051</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>45714</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45182</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>45897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45443</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45689</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45363</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45817</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>46141</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>45516</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44798</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>46021</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>45214</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46079</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45909</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44881</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45600</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>45520</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>45533</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14631,7 +14631,7 @@
         <v>46149</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45665</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44980</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45933</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>45932</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45932</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45453</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45937</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45350</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>45939</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45939</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45939</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45939</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45945</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>46154</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45238</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>44970</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>45772</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>45945</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>45950</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>45952</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45646</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>45956</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>45956</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>46154</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44972</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>45890</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
         <v>45959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45961</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>46161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45772</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45520</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45964</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45965</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17183,7 +17183,7 @@
         <v>45965</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45601</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45966</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>44980</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45974</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45331</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44612</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45691</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>46164</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45981</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>46164</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>45322</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45596</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45986</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>45309</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45987</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>45169</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45471</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>44509</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45712</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45604</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45994</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>44966</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45481</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>46002</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>45457</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>46174</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45002</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45614</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45183</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45106</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>46169</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>46031</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44503</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46033</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45315</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46034</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>46036</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46037</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45589</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>46042</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>44960</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>46044</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>46049</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46048</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46049</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>46051</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>46050</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>45204</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45085</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>46052</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46181</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>46183</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>46057</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>46058</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45582</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>46058</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>46062</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46041</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>46184</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45666</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>46021</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45240</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45639</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45673</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>44734</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>46071</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>46188</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>46188</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>46188</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>46084</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>46082</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46082</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46190</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>46090</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44546</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>46190</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45147</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45187</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>46184</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>46188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46188</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>46094</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>46094</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>46094</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>46191</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>46094</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45166</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>46092</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45644</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>46195</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45174</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46106</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44739</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>46108</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>46112</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45363</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>46114</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>44869</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>46113</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>46119</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>46199</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>46121</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         <v>46120</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>46121</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45749</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>46120</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>46121</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44805</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>46120</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45299</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>46124</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45689</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45689</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>46125</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45631</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45244</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>46128</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46128</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26367,7 +26367,7 @@
         <v>46127</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>46127</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>46127</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>44908</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>46128</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>46127</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>46202</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46204</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>46204</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45225</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46135</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45817</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46204</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>46203</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46203</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>46204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>46139</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45940</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44701</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45296</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45775</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45008</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46210</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45448</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>46210</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>46212</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46212</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>46199</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44930</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45265</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>45471</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>46034</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>46272</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>46272</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>46272</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45372</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>46275</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         <v>46275</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>46275</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45184</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46275</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>46274</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>46231</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45082</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44867</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44837</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45754</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>46276</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>44673</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>46276</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45240</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45519</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>46281</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>46280</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>46280</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>46280</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>46280</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>46238</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45222</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46281</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>44855</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>46281</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>45244</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>44909</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>46283</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>46283</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45331</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>45254</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45371</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>44930</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31808,7 +31808,7 @@
         <v>45244</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>46286</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45631</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45735</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46288</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46289</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45247</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>44931</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
         <v>45588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45763</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45169</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>46290</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>45491</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>46293</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45672</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45762</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45722</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45700</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>46252</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>46252</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46294</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33459,7 +33459,7 @@
         <v>46294</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33537,7 +33537,7 @@
         <v>46293</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>46252</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>46294</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33771,7 +33771,7 @@
         <v>46294</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46294</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>46253</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>44916</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>46297</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>46254</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>46253</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>46253</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>46253</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>46297</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46253</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46253</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>46191</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45215</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45215</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>46300</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>46300</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>46062</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45783</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46300</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45674</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45783</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46255</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45483</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45492</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>44719</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46300</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46303</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35910,7 +35910,7 @@
         <v>46259</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>46302</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>46303</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>46302</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46259</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45793</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45688</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>46307</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45483</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>46262</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45531</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36738,7 +36738,7 @@
         <v>45890</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45798</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>46304</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>46304</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46191</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>46261</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>46308</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         <v>46266</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37337,7 +37337,7 @@
         <v>46309</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37415,7 +37415,7 @@
         <v>46309</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>46308</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45807</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45807</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>46308</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>46265</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45811</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45811</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>45695</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>46268</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         <v>46268</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38248,7 +38248,7 @@
         <v>45819</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45824</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>46268</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38477,7 +38477,7 @@
         <v>45832</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38550,7 +38550,7 @@
         <v>45833</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45833</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45835</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45840</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45840</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45840</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38998,7 +38998,7 @@
         <v>45846</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>45854</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45756</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39217,7 +39217,7 @@
         <v>45860</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45754</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45868</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39446,7 +39446,7 @@
         <v>45876</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45876</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>45401</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44802</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45208</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45699</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>46035</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>46089</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>

--- a/Översikt VANSBRO.xlsx
+++ b/Översikt VANSBRO.xlsx
@@ -601,7 +601,7 @@
         <v>45492</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>44820</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         <v>45938</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45987</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>45880</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46303</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>46014</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45982</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>45727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>46007</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>46128</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>45842</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46052</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>46197</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45842</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46052</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>45840</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46042</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>44504</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45576</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>46083</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45840</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>45735</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45735</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>45322</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>46301</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46302</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>45813</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45409</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>45726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44790</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>45735</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>46034</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>46251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>46134</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46316</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45394</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45247</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45933</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45617</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>46184</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>45518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>46043</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>46051</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45811</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>45839</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46136</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45956</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>45247</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44942</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>45377</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44881</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44753</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44519</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>44830</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44519</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44708</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44742</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44790</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44880</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>44826</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44672</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44739</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44790</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44774</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44614</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44817</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44790</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44732</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44827</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>44748</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44643</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>45888</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45888</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44812</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44754</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44816</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45888</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44970</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44673</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44881</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45448</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44930</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45897</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>44811</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44739</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45904</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45240</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45240</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>44855</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45884</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>44796</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>46161</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>45214</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45909</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45331</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45471</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>46164</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>45576</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>46164</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45363</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45689</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45932</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>44980</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45932</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>45063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>45238</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44931</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         <v>46174</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>45614</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         <v>45933</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45937</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>45939</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         <v>45939</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>45939</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>45939</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45749</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44837</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>45589</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>45945</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>45315</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>46169</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>45945</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45533</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44980</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45950</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>46181</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45952</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45141</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>45169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45956</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45956</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45959</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45512</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>46184</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44791</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>46188</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45296</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45964</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45961</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>46190</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>46188</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>46188</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45965</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>46190</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45966</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>46191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45965</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>46188</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>46184</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>46188</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>44612</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>44798</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>46195</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45972</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>46197</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45722</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45519</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>45974</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>46199</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>44503</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>45453</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>46203</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45666</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>46202</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>46203</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45754</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>46204</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45981</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45712</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>46204</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>44880</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>46204</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45258</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45309</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45987</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>44862</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>46210</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45204</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46210</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44546</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45182</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>45588</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45994</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46212</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>46199</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>46212</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45457</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>46002</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45443</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46034</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>46231</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>45483</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45783</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45674</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45783</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>46280</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>44719</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>46280</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45492</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>46280</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>46280</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>46281</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>46281</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>46281</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>46281</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>46238</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>46034</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45483</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>46033</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>46031</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>46286</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>46036</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45793</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>46283</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>46283</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46037</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>46042</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45688</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>46044</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>45531</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46288</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45798</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>46050</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>46049</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>46048</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>46049</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>46289</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46052</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>46051</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>46058</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>46058</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>46057</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45807</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>46290</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>45807</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>46294</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45582</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>46062</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45811</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45811</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45222</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>46293</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45695</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22047,7 +22047,7 @@
         <v>46041</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>46294</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>46293</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45666</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45639</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>46294</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>44734</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45240</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46021</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>46294</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>45673</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>46071</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22943,7 +22943,7 @@
         <v>46294</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>46252</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>45819</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>46253</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45824</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>46253</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>46253</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>46252</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>46253</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>46082</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>46253</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>46253</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>46252</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>46082</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45832</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>46084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>46300</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45833</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>46300</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45833</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>46297</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>46090</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45835</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>46300</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46254</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>46297</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>46062</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45840</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45840</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45840</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>46094</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>46094</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>46094</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>46094</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>46255</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>46300</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>46191</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>45846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25837,7 +25837,7 @@
         <v>46302</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>46092</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>46259</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45377</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>46259</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45854</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>46106</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>45860</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46302</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>46108</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45756</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>46304</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>46304</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>46112</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45754</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26957,7 +26957,7 @@
         <v>46114</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>46113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45516</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>46119</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45868</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>46303</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>46120</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>46121</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>46121</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>46120</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>46120</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>46121</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>46303</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>46124</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>46125</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45174</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>46261</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>46127</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>46127</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>46127</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>46127</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45876</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45876</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46128</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>46128</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>46308</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>46265</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>46128</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45644</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>46307</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45890</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>46308</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45106</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45532</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>44509</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>46191</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45817</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45491</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29811,7 +29811,7 @@
         <v>46135</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>45646</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>45544</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>46262</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>46308</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>45776</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30269,7 +30269,7 @@
         <v>45806</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         <v>46309</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>46309</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>46266</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>46139</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45811</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>46268</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>46268</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45440</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45183</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>46268</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>45727</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45714</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>46272</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31331,7 +31331,7 @@
         <v>46272</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>46272</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>46315</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>46051</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45689</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45940</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>46021</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>46275</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>46318</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45604</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45363</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>46274</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45817</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>46275</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>46318</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>46318</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>46141</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
         <v>46276</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>46276</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45772</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>46079</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>46275</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>46275</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45498</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>44966</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45085</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46149</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45082</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45350</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>44701</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>46154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>46154</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33752,7 +33752,7 @@
         <v>45184</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45890</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45772</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45689</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45617</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45299</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>45244</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45601</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>45481</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45637</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45166</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45631</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44869</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>45672</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
         <v>44820</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34930,7 +34930,7 @@
         <v>45646</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45225</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45691</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45691</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>44957</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45189</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>45530</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>45763</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>45764</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>45735</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>45689</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45689</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>44972</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>44908</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45222</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44960</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45371</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>44909</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45247</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45520</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>45530</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45002</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>44925</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>45471</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45443</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45331</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45600</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45078</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45372</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>44805</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>45194</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>44648</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45665</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>45762</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>45244</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>45147</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>45700</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>44728</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>44728</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45183</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45183</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45665</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>45463</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>45169</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>45187</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>44867</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45744</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>45215</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45215</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>45754</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>45254</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>45322</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>45254</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>44930</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38952,7 +38952,7 @@
         <v>44886</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>45775</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>45265</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>45315</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>45726</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45520</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39395,7 +39395,7 @@
         <v>45531</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>44916</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45008</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44960</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>44826</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>45401</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44802</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>45208</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>45699</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>46035</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>46089</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
